--- a/AtchisonRegime/Outputs/China/ASX300/df_regSummary_ASX300.xlsx
+++ b/AtchisonRegime/Outputs/China/ASX300/df_regSummary_ASX300.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3840496030387139</v>
+        <v>0.2351237710555614</v>
       </c>
       <c r="H2" t="n">
-        <v>3.401990645089062</v>
+        <v>3.412591696523912</v>
       </c>
       <c r="I2" t="n">
         <v>-3.79110563625414</v>
@@ -545,19 +545,19 @@
         <v>10.2113173457014</v>
       </c>
       <c r="K2" t="n">
-        <v>24</v>
+        <v>24.75247524752475</v>
       </c>
       <c r="L2" t="n">
         <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01821100348290232</v>
+        <v>0.01168289274284049</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0529738859666341</v>
+        <v>-0.05511394832336292</v>
       </c>
       <c r="P2" t="n">
         <v>0.141968811866646</v>
@@ -603,7 +603,7 @@
         <v>8.779535078076917</v>
       </c>
       <c r="K3" t="n">
-        <v>23</v>
+        <v>22.77227722772277</v>
       </c>
       <c r="L3" t="n">
         <v>4</v>
@@ -661,7 +661,7 @@
         <v>7.257145141894861</v>
       </c>
       <c r="K4" t="n">
-        <v>30</v>
+        <v>29.7029702970297</v>
       </c>
       <c r="L4" t="n">
         <v>3</v>
@@ -719,7 +719,7 @@
         <v>6.042936784522324</v>
       </c>
       <c r="K5" t="n">
-        <v>23</v>
+        <v>22.77227722772277</v>
       </c>
       <c r="L5" t="n">
         <v>3</v>
